--- a/SJ/SB01_NOW/SB01_ComparisonTable.xlsx
+++ b/SJ/SB01_NOW/SB01_ComparisonTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\sb01_dashboard-main\SJ\SB01_NOW\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\產學合作\SB01_NOW-20250729\SB01_NOW\SB01-RAW_OK\sliding_window_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56C8846-40F1-4EC1-AC4B-83667B6ED5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF75DC43-3BF4-48B0-B188-C929099661B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1440" windowWidth="15250" windowHeight="12110" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1F" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="136">
   <si>
     <t>DCC_name</t>
   </si>
@@ -392,11 +392,63 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Inappropriate1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inappropriate2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inappropriate3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>original1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Inappropriate</t>
+    <t>TTHT153</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TTHT103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Correlation5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Correlation6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TTHT204</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TTHT206</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TTHT214</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Correlation7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TTHT402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TTHT409</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TTHT422</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -501,7 +553,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -626,21 +678,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
-        <color rgb="FFFF0000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FFFF0000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FFFF0000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -664,17 +701,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -714,46 +740,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FFFF0000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FFFF0000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -800,121 +793,70 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="17" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -935,9 +877,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -975,7 +917,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1081,7 +1023,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1223,7 +1165,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1231,17 +1173,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K20"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" style="1" customWidth="1"/>
+    <col min="10" max="12" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1266,441 +1209,485 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="I1" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="K1" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="J1" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="K1" s="30" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="L1" s="24" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="17"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="31" t="s">
+      <c r="F2" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="31" t="s">
+      <c r="K2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="31" t="s">
+      <c r="L2" s="25" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="31" t="s">
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-    </row>
-    <row r="4" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="E4" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="17"/>
+      <c r="G4" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="48"/>
-      <c r="I4" s="31" t="s">
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="31" t="s">
+      <c r="K4" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="31" t="s">
+      <c r="L4" s="25" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="38"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="32" t="s">
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="H5" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="48" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-    </row>
-    <row r="6" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="I5" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="43"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="31" t="s">
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-    </row>
-    <row r="7" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="25" t="s">
         <v>12</v>
       </c>
       <c r="F7" s="17"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="31" t="s">
+      <c r="G7" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="31" t="s">
+      <c r="K7" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="31" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="L7" s="25"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="38"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="32" t="s">
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="48"/>
-      <c r="I8" s="31" t="s">
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-    </row>
-    <row r="9" spans="1:11" ht="16.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+    </row>
+    <row r="9" spans="1:12" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="42"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="48"/>
-      <c r="I9" s="31" t="s">
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="31"/>
+      <c r="J9" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-    </row>
-    <row r="10" spans="1:11" ht="17.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+    </row>
+    <row r="10" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="28"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="54" t="s">
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="54"/>
-      <c r="K10" s="54"/>
-    </row>
-    <row r="11" spans="1:11" ht="17.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G10" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="37"/>
+    </row>
+    <row r="11" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="28"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="54" t="s">
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="54"/>
-      <c r="K11" s="54"/>
-    </row>
-    <row r="12" spans="1:11" ht="16.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G11" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37"/>
+      <c r="L11" s="37"/>
+    </row>
+    <row r="12" spans="1:12" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="C12" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="44"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="52" t="s">
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="J12" s="52"/>
-      <c r="K12" s="52"/>
-    </row>
-    <row r="13" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="34" t="s">
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="G13" s="34" t="s">
+      <c r="G13" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="50"/>
-      <c r="I13" s="52" t="s">
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="52"/>
-      <c r="K13" s="52"/>
-    </row>
-    <row r="14" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="44"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="52" t="s">
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="J14" s="52"/>
-      <c r="K14" s="52"/>
-    </row>
-    <row r="15" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="45" t="s">
+      <c r="C15" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="44"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="52" t="s">
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="J15" s="52"/>
-      <c r="K15" s="52"/>
-    </row>
-    <row r="16" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="45" t="s">
+      <c r="C16" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="44"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="52" t="s">
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="52"/>
-      <c r="K16" s="52"/>
-    </row>
-    <row r="17" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G16" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="H16" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16" s="33"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="45" t="s">
+      <c r="C17" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="44"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="52" t="s">
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="H17" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
-    </row>
-    <row r="18" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="I17" s="33"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="45" t="s">
+      <c r="C18" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="44"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="52" t="s">
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="J18" s="52"/>
-      <c r="K18" s="52"/>
-    </row>
-    <row r="19" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="45" t="s">
+      <c r="C19" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="44"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="52" t="s">
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="J19" s="52"/>
-      <c r="K19" s="52"/>
-    </row>
-    <row r="20" spans="1:11" ht="17.5" thickTop="1" x14ac:dyDescent="0.4"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1709,18 +1696,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="11.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1728,7 +1716,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>5</v>
@@ -1745,748 +1733,943 @@
       <c r="H1" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="30" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="I1" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="25" t="s">
         <v>42</v>
       </c>
       <c r="D2" s="17"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="31" t="s">
+      <c r="E2" s="26" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="F2" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="25"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" s="48" t="s">
+      <c r="G3" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="31"/>
-    </row>
-    <row r="4" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="I3" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="J3" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="K3" s="25"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="25" t="s">
         <v>44</v>
       </c>
       <c r="D4" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="31" t="s">
+      <c r="F4" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="H4" s="26" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="25"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="25" t="s">
         <v>46</v>
       </c>
       <c r="D5" s="17"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="48"/>
+      <c r="E5" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>129</v>
+      </c>
       <c r="I5" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="31"/>
+      <c r="K5" s="25" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="25" t="s">
         <v>46</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="31" t="s">
+      <c r="F6" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="26"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="25" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="31" t="s">
+      <c r="D7" s="17"/>
+      <c r="E7" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="25" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="48"/>
+      <c r="D8" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="26" t="s">
+        <v>48</v>
+      </c>
       <c r="I8" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="J8" s="31"/>
+      <c r="K8" s="25" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>50</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D9" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="48"/>
+      <c r="F9" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="26" t="s">
+        <v>48</v>
+      </c>
       <c r="I9" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="J9" s="31"/>
+      <c r="K9" s="25" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="25" t="s">
         <v>51</v>
       </c>
       <c r="D10" s="17"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="31" t="s">
+      <c r="E10" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="25" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="48"/>
+      <c r="D11" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="26" t="s">
+        <v>48</v>
+      </c>
       <c r="I11" s="31" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+        <v>129</v>
+      </c>
+      <c r="J11" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" s="25"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="25" t="s">
         <v>45</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="G12" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="31" t="s">
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="25" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="25" t="s">
         <v>45</v>
       </c>
       <c r="D13" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="F13" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="32"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="31" t="s">
+      <c r="G13" s="26"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="25" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="25" t="s">
         <v>53</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="G14" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" s="48" t="s">
+      <c r="I14" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="J14" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="I14" s="31" t="s">
+      <c r="K14" s="25" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="25" t="s">
         <v>53</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="32" t="s">
+      <c r="G15" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="32"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="31" t="s">
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="25" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>38</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="25" t="s">
         <v>53</v>
       </c>
       <c r="D16" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="31" t="s">
+      <c r="G16" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="25" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="45" t="s">
+      <c r="B17" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="52" t="s">
+      <c r="D17" s="19"/>
+      <c r="E17" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="35" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="45" t="s">
+      <c r="B18" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="52" t="s">
+      <c r="D18" s="19"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="35" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" s="45" t="s">
+      <c r="B19" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="52" t="s">
+      <c r="D19" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" s="28" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G19" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="35"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="45" t="s">
+      <c r="B20" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="52" t="s">
+      <c r="D20" s="28" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E20" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="G20" s="28"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="35"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="45" t="s">
+      <c r="B21" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="52" t="s">
+      <c r="D21" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" s="28"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="35" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="45" t="s">
+      <c r="B22" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="52" t="s">
+      <c r="D22" s="19"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="35" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="45" t="s">
+      <c r="B23" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E23" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F23" s="34" t="s">
+      <c r="F23" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="G23" s="34"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="52" t="s">
+      <c r="G23" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="H23" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="35" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="45" t="s">
+      <c r="B24" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="52" t="s">
+      <c r="D24" s="19"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="35" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="45" t="s">
+      <c r="B25" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="E25" s="34" t="s">
+      <c r="E25" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="52" t="s">
+      <c r="F25" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="G25" s="28" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="35"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="45" t="s">
+      <c r="B26" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="E26" s="34" t="s">
+      <c r="E26" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="F26" s="34" t="s">
+      <c r="F26" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="G26" s="34"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="52" t="s">
+      <c r="G26" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="H26" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="35" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="45" t="s">
+      <c r="B27" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="E27" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="52" t="s">
+      <c r="D27" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="35" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="45" t="s">
+      <c r="B28" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="19"/>
+      <c r="E28" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="E28" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="52" t="s">
+      <c r="F28" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G28" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="35" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="45" t="s">
+      <c r="B29" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="D29" s="19"/>
+      <c r="E29" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E29" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="50"/>
-      <c r="I29" s="52" t="s">
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="35" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="45" t="s">
+      <c r="B30" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="D30" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="E30" s="34" t="s">
+      <c r="E30" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="34" t="s">
+      <c r="F30" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="G30" s="34"/>
-      <c r="H30" s="50"/>
-      <c r="I30" s="52" t="s">
+      <c r="G30" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="35" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="45" t="s">
+      <c r="B31" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="D31" s="20" t="s">
+      <c r="D31" s="19"/>
+      <c r="E31" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="52" t="s">
+      <c r="F31" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G31" s="28"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="35" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B32" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" s="45" t="s">
+      <c r="B32" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="D32" s="19"/>
+      <c r="E32" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="E32" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="F32" s="34" t="s">
+      <c r="F32" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="G32" s="34"/>
-      <c r="H32" s="50"/>
-      <c r="I32" s="52" t="s">
+      <c r="G32" s="28"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="35" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B33" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C33" s="45" t="s">
+      <c r="B33" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="D33" s="20" t="s">
+      <c r="D33" s="19"/>
+      <c r="E33" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E33" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="50"/>
-      <c r="I33" s="52" t="s">
+      <c r="F33" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="G33" s="28"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="35" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B34" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="45" t="s">
+      <c r="B34" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="D34" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="E34" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E34" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="50"/>
-      <c r="I34" s="52" t="s">
+      <c r="F34" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="H34" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="I34" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="J34" s="33"/>
+      <c r="K34" s="35" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="17.5" thickTop="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2495,19 +2678,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:L34"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="11.88671875" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -2515,7 +2699,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>5</v>
@@ -2529,643 +2713,826 @@
       <c r="G1" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="H1" s="30" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="H1" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>40</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="25" t="s">
         <v>76</v>
       </c>
       <c r="D2" s="17"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="31" t="s">
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="25" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="25" t="s">
         <v>76</v>
       </c>
       <c r="D3" s="17"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="31" t="s">
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="25" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="25" t="s">
         <v>76</v>
       </c>
       <c r="D4" s="17"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="31" t="s">
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="25" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="25" t="s">
         <v>76</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="32" t="s">
-        <v>78</v>
-      </c>
-      <c r="F5" s="32" t="s">
+      <c r="E5" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="48"/>
-      <c r="H5" s="31" t="s">
+      <c r="F5" s="26"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="25" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>26</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="31" t="s">
+      <c r="D6" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="26"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="25" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>47</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="25" t="s">
         <v>79</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="48"/>
-      <c r="H7" s="31" t="s">
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="25" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>49</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="25" t="s">
         <v>80</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="G8" s="48"/>
-      <c r="H8" s="31" t="s">
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="25" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>50</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="E9" s="32" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="G9" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="H9" s="31"/>
-    </row>
-    <row r="10" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="25" t="s">
         <v>80</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="F10" s="32"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="31" t="s">
+      <c r="F10" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="25" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="25" t="s">
         <v>81</v>
       </c>
       <c r="D11" s="17"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="31" t="s">
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="25" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>52</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="31" t="s">
+      <c r="D12" s="26" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E12" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="25"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
         <v>36</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="25" t="s">
         <v>83</v>
       </c>
       <c r="D13" s="17"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="31" t="s">
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="25" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>37</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="I14" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J14" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="F14" s="32"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="31" t="s">
+      <c r="K14" s="17" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="L14" s="25"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>38</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="25" t="s">
         <v>81</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="F15" s="32" t="s">
+      <c r="E15" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="48"/>
-      <c r="H15" s="31" t="s">
+      <c r="F15" s="26"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="25" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>39</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="25" t="s">
         <v>82</v>
       </c>
       <c r="D16" s="17"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="31" t="s">
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="25" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="45" t="s">
+      <c r="B17" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="52" t="s">
+      <c r="D17" s="19"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="35" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="45" t="s">
+      <c r="B18" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="52" t="s">
+      <c r="D18" s="19"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="35" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" s="45" t="s">
+      <c r="B19" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="52" t="s">
+      <c r="D19" s="19"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="35" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="45" t="s">
+      <c r="B20" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="52" t="s">
+      <c r="D20" s="19"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="35" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="45" t="s">
+      <c r="B21" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="52" t="s">
+      <c r="D21" s="19"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="35" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="45" t="s">
+      <c r="B22" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="52" t="s">
+      <c r="D22" s="19"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="35" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B23" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="45" t="s">
+      <c r="B23" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="52" t="s">
+      <c r="D23" s="19"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="35" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="45" t="s">
+      <c r="B24" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="52" t="s">
+      <c r="D24" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="G24" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="35" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="45" t="s">
+      <c r="B25" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="52" t="s">
+      <c r="D25" s="19"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="35" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="45" t="s">
+      <c r="B26" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="52" t="s">
+      <c r="D26" s="19"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="35" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="45" t="s">
+      <c r="B27" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="52" t="s">
+      <c r="D27" s="19"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="35" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="45" t="s">
+      <c r="B28" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="52" t="s">
+      <c r="D28" s="19"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="35" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="45" t="s">
+      <c r="B29" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="52" t="s">
+      <c r="D29" s="28" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E29" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="35"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="45" t="s">
+      <c r="B30" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="52" t="s">
+      <c r="D30" s="19"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="35" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="45" t="s">
+      <c r="B31" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="52" t="s">
+      <c r="D31" s="28" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E31" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="28"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="35"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" s="45" t="s">
+      <c r="B32" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="52" t="s">
+      <c r="D32" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E32" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" s="28"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="35" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B33" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C33" s="45" t="s">
+      <c r="B33" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="52" t="s">
+      <c r="D33" s="19"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="35" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B34" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="45" t="s">
+      <c r="B34" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="52" t="s">
+      <c r="D34" s="19"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="35" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="17.5" thickTop="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3174,18 +3541,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H44"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:L43"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="11.88671875" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3193,7 +3561,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>5</v>
@@ -3207,841 +3575,1096 @@
       <c r="G1" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="H1" s="30" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="H1" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="25" t="s">
         <v>95</v>
       </c>
       <c r="D2" s="17"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="31" t="s">
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="25" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="25" t="s">
         <v>95</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="G3" s="48"/>
-      <c r="H3" s="31" t="s">
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="25" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="25" t="s">
         <v>96</v>
       </c>
       <c r="D4" s="17"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="31" t="s">
+      <c r="E4" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" s="26"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="25" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="17"/>
+      <c r="E5" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="E5" s="32" t="s">
-        <v>95</v>
-      </c>
-      <c r="F5" s="32"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="31" t="s">
+      <c r="F5" s="26"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="25" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="F6" s="32"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="31" t="s">
+      <c r="D6" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="25" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="25" t="s">
         <v>98</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="G7" s="48"/>
-      <c r="H7" s="31" t="s">
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="25" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="31" t="s">
+      <c r="D8" s="26" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E8" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" s="26"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="25"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="25" t="s">
         <v>95</v>
       </c>
       <c r="D9" s="17"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="31" t="s">
+      <c r="E9" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="26"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="25" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>50</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="31" t="s">
+      <c r="D10" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="25" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="F11" s="32"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="31" t="s">
+      <c r="D11" s="17"/>
+      <c r="E11" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" s="26"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="25" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="25" t="s">
         <v>98</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="F12" s="32"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="31" t="s">
+      <c r="F12" s="26"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="25" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="25" t="s">
         <v>98</v>
       </c>
       <c r="D13" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="F13" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="H13" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="I13" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="G13" s="48"/>
-      <c r="H13" s="31" t="s">
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="25" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="25" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="E14" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="F14" s="32"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="31" t="s">
+      <c r="E14" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" s="26"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="25" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="F15" s="32"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="31" t="s">
+      <c r="D15" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" s="26"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="25" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="25" t="s">
         <v>101</v>
       </c>
       <c r="D16" s="17"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="31" t="s">
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="25" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="31" t="s">
+      <c r="D17" s="26"/>
+      <c r="E17" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="26"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="25" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D18" s="17"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="31" t="s">
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="25" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="37" t="s">
+      <c r="C19" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="17"/>
+      <c r="E19" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="E19" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="F19" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="48" t="s">
+      <c r="G19" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="H19" s="31" t="s">
+      <c r="H19" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="I19" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="25" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C20" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="31" t="s">
+      <c r="D20" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="25" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C21" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="17"/>
+      <c r="E21" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="E21" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="F21" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="G21" s="48"/>
-      <c r="H21" s="31" t="s">
+      <c r="F21" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="G21" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="25" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C22" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D22" s="17"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="31" t="s">
+      <c r="E22" s="26" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="F22" s="26"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="25"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="D23" s="22"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="51" t="s">
+      <c r="D23" s="21"/>
+      <c r="E23" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="F23" s="29"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="34" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="46" t="s">
+      <c r="C24" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="D24" s="22"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="51" t="s">
+      <c r="D24" s="21"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="34" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="46" t="s">
+      <c r="C25" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="D25" s="22"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="51" t="s">
+      <c r="D25" s="21"/>
+      <c r="E25" s="29" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="F25" s="29"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="34"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="45" t="s">
+      <c r="B26" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="52" t="s">
+      <c r="D26" s="19"/>
+      <c r="E26" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="35" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="45" t="s">
+      <c r="B27" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="52" t="s">
+      <c r="D27" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="E27" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="F27" s="28"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="35" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="45" t="s">
+      <c r="B28" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="52" t="s">
+      <c r="D28" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="F28" s="28"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="35" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="45" t="s">
+      <c r="B29" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="52" t="s">
+      <c r="D29" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="F29" s="28" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="35"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="45" t="s">
+      <c r="B30" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="52" t="s">
+      <c r="D30" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="F30" s="28"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="35" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B31" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="45" t="s">
+      <c r="B31" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="52" t="s">
+      <c r="D31" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="E31" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="F31" s="28"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="35" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" s="47" t="s">
+      <c r="B32" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="D32" s="34" t="s">
+      <c r="D32" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="E32" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F32" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="E32" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="F32" s="34" t="s">
+      <c r="G32" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="G32" s="50" t="s">
+      <c r="H32" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="H32" s="52"/>
-    </row>
-    <row r="33" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="I32" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="35"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B33" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C33" s="45" t="s">
+      <c r="B33" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="52" t="s">
+      <c r="D33" s="19"/>
+      <c r="E33" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="F33" s="28"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="35" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="45" t="s">
+      <c r="B34" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="52" t="s">
+      <c r="D34" s="19"/>
+      <c r="E34" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="F34" s="28"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="35" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="45" t="s">
+      <c r="B35" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="52" t="s">
+      <c r="D35" s="19"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="33"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="33"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="33"/>
+      <c r="L35" s="35" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" s="45" t="s">
+      <c r="B36" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="52" t="s">
+      <c r="D36" s="19"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="35" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B37" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" s="45" t="s">
+      <c r="B37" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="52" t="s">
+      <c r="D37" s="19"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33"/>
+      <c r="K37" s="33"/>
+      <c r="L37" s="35" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" s="45" t="s">
+      <c r="B38" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="D38" s="20"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="52" t="s">
+      <c r="D38" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="E38" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="F38" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="33"/>
+      <c r="L38" s="35" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B39" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" s="45" t="s">
+      <c r="B39" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="D39" s="20"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="52" t="s">
+      <c r="D39" s="19"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="35" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B40" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" s="45" t="s">
+      <c r="B40" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="D40" s="20"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="50"/>
-      <c r="H40" s="52" t="s">
+      <c r="D40" s="19"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
+      <c r="J40" s="33"/>
+      <c r="K40" s="33"/>
+      <c r="L40" s="35" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B41" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" s="45" t="s">
+      <c r="B41" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="D41" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="E41" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="F41" s="34"/>
-      <c r="G41" s="50"/>
-      <c r="H41" s="52" t="s">
+      <c r="D41" s="19"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33"/>
+      <c r="I41" s="33"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="33"/>
+      <c r="L41" s="35" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B42" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C42" s="45" t="s">
+      <c r="B42" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="D42" s="20"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="50"/>
-      <c r="H42" s="52" t="s">
+      <c r="D42" s="19"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="33"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="35" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B43" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C43" s="45" t="s">
+      <c r="B43" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="D43" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="E43" s="34" t="s">
+      <c r="D43" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="E43" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="F43" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="G43" s="50" t="s">
+      <c r="F43" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="G43" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="H43" s="52" t="s">
+      <c r="H43" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="I43" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="J43" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="K43" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="L43" s="35" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="17.5" thickTop="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
